--- a/test/fixtures/xlsx/core/core.xlsx
+++ b/test/fixtures/xlsx/core/core.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="229">
   <si>
     <t xml:space="preserve">~~enum:ValueType~~</t>
   </si>
@@ -678,6 +678,33 @@
   </si>
   <si>
     <t xml:space="preserve">grade assigned when unspecified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SeasonStart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-01 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when the season opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RoundLength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">length of one round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BuildId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6f9619ff-8b86-d011-b42d-00c04fc964ff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identifies this data build</t>
   </si>
 </sst>
 </file>
@@ -2040,7 +2067,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:F9"/>
+  <dimension ref="B2:F12"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -2155,6 +2182,57 @@
         <v>219</v>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F10" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>224</v>
+      </c>
+      <c r="F11" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F12" t="s">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
